--- a/templates/deliverable/example/10_인덱스정의서.xlsx
+++ b/templates/deliverable/example/10_인덱스정의서.xlsx
@@ -20,10 +20,10 @@
     <t>순번</t>
   </si>
   <si>
-    <t>DB명</t>
+    <t>영문 DB명</t>
   </si>
   <si>
-    <t>테이블명</t>
+    <t>영문 테이블명</t>
   </si>
   <si>
     <t>인덱스명</t>
@@ -59,12 +59,12 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <sz val="11.0"/>
+      <sz val="14.0"/>
       <b val="true"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <sz val="14.0"/>
+      <sz val="11.0"/>
       <b val="true"/>
     </font>
   </fonts>
@@ -118,8 +118,8 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true"/>
   </cellXfs>
 </styleSheet>
@@ -131,8 +131,8 @@
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="8.0" customWidth="true"/>
-    <col min="2" max="2" width="10.0" customWidth="true"/>
-    <col min="3" max="3" width="12.0" customWidth="true"/>
+    <col min="2" max="2" width="16.0" customWidth="true"/>
+    <col min="3" max="3" width="18.0" customWidth="true"/>
     <col min="4" max="4" width="12.0" customWidth="true"/>
     <col min="5" max="5" width="14.0" customWidth="true"/>
     <col min="6" max="6" width="12.0" customWidth="true"/>
